--- a/artfynd/A 34033-2023 artfynd.xlsx
+++ b/artfynd/A 34033-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122545730</v>
+        <v>122545731</v>
       </c>
       <c r="B2" t="n">
-        <v>78652</v>
+        <v>56593</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100138</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601927</v>
+        <v>601928</v>
       </c>
       <c r="R2" t="n">
-        <v>7295333</v>
+        <v>7295474</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +790,7 @@
         <v>122545726</v>
       </c>
       <c r="B3" t="n">
-        <v>77584</v>
+        <v>77588</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,6 +804,11 @@
       </c>
       <c r="E3" t="n">
         <v>6487</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -892,7 +902,7 @@
         <v>122545728</v>
       </c>
       <c r="B4" t="n">
-        <v>78036</v>
+        <v>78040</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,6 +916,11 @@
       </c>
       <c r="E4" t="n">
         <v>6437</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -996,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122545731</v>
+        <v>122545730</v>
       </c>
       <c r="B5" t="n">
-        <v>56589</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,20 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601928</v>
+        <v>601927</v>
       </c>
       <c r="R5" t="n">
-        <v>7295474</v>
+        <v>7295333</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 34033-2023 artfynd.xlsx
+++ b/artfynd/A 34033-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122545731</v>
+        <v>122545728</v>
       </c>
       <c r="B2" t="n">
-        <v>56593</v>
+        <v>78040</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601928</v>
+        <v>601927</v>
       </c>
       <c r="R2" t="n">
-        <v>7295474</v>
+        <v>7295329</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122545728</v>
+        <v>122545731</v>
       </c>
       <c r="B4" t="n">
-        <v>78040</v>
+        <v>56593</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601927</v>
+        <v>601928</v>
       </c>
       <c r="R4" t="n">
-        <v>7295329</v>
+        <v>7295474</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 34033-2023 artfynd.xlsx
+++ b/artfynd/A 34033-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122545726</v>
+        <v>122545730</v>
       </c>
       <c r="B3" t="n">
-        <v>77588</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601967</v>
+        <v>601927</v>
       </c>
       <c r="R3" t="n">
-        <v>7295329</v>
+        <v>7295333</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122545731</v>
+        <v>122545726</v>
       </c>
       <c r="B4" t="n">
-        <v>56593</v>
+        <v>77588</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601928</v>
+        <v>601967</v>
       </c>
       <c r="R4" t="n">
-        <v>7295474</v>
+        <v>7295329</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122545730</v>
+        <v>122545731</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601927</v>
+        <v>601928</v>
       </c>
       <c r="R5" t="n">
-        <v>7295333</v>
+        <v>7295474</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 34033-2023 artfynd.xlsx
+++ b/artfynd/A 34033-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122545728</v>
+        <v>122545730</v>
       </c>
       <c r="B2" t="n">
-        <v>78040</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,7 +718,7 @@
         <v>601927</v>
       </c>
       <c r="R2" t="n">
-        <v>7295329</v>
+        <v>7295333</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122545730</v>
+        <v>122545731</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>56593</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601927</v>
+        <v>601928</v>
       </c>
       <c r="R3" t="n">
-        <v>7295333</v>
+        <v>7295474</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122545731</v>
+        <v>122545728</v>
       </c>
       <c r="B5" t="n">
-        <v>56593</v>
+        <v>78040</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601928</v>
+        <v>601927</v>
       </c>
       <c r="R5" t="n">
-        <v>7295474</v>
+        <v>7295329</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 34033-2023 artfynd.xlsx
+++ b/artfynd/A 34033-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122545731</v>
+        <v>122545726</v>
       </c>
       <c r="B3" t="n">
-        <v>56593</v>
+        <v>77588</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601928</v>
+        <v>601967</v>
       </c>
       <c r="R3" t="n">
-        <v>7295474</v>
+        <v>7295329</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122545726</v>
+        <v>122545728</v>
       </c>
       <c r="B4" t="n">
-        <v>77588</v>
+        <v>78040</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601967</v>
+        <v>601927</v>
       </c>
       <c r="R4" t="n">
         <v>7295329</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122545728</v>
+        <v>122545731</v>
       </c>
       <c r="B5" t="n">
-        <v>78040</v>
+        <v>56593</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601927</v>
+        <v>601928</v>
       </c>
       <c r="R5" t="n">
-        <v>7295329</v>
+        <v>7295474</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 34033-2023 artfynd.xlsx
+++ b/artfynd/A 34033-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122545730</v>
+        <v>122545726</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>77589</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601927</v>
+        <v>601967</v>
       </c>
       <c r="R2" t="n">
-        <v>7295333</v>
+        <v>7295329</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122545726</v>
+        <v>122545731</v>
       </c>
       <c r="B3" t="n">
-        <v>77588</v>
+        <v>56594</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601967</v>
+        <v>601928</v>
       </c>
       <c r="R3" t="n">
-        <v>7295329</v>
+        <v>7295474</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122545728</v>
+        <v>122545730</v>
       </c>
       <c r="B4" t="n">
-        <v>78040</v>
+        <v>78657</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,7 +942,7 @@
         <v>601927</v>
       </c>
       <c r="R4" t="n">
-        <v>7295329</v>
+        <v>7295333</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122545731</v>
+        <v>122545728</v>
       </c>
       <c r="B5" t="n">
-        <v>56593</v>
+        <v>78041</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601928</v>
+        <v>601927</v>
       </c>
       <c r="R5" t="n">
-        <v>7295474</v>
+        <v>7295329</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 34033-2023 artfynd.xlsx
+++ b/artfynd/A 34033-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122545726</v>
+        <v>122545731</v>
       </c>
       <c r="B2" t="n">
-        <v>77589</v>
+        <v>56594</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601967</v>
+        <v>601928</v>
       </c>
       <c r="R2" t="n">
-        <v>7295329</v>
+        <v>7295474</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122545731</v>
+        <v>122545730</v>
       </c>
       <c r="B3" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601928</v>
+        <v>601927</v>
       </c>
       <c r="R3" t="n">
-        <v>7295474</v>
+        <v>7295333</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122545730</v>
+        <v>122545728</v>
       </c>
       <c r="B4" t="n">
-        <v>78657</v>
+        <v>78044</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,7 +942,7 @@
         <v>601927</v>
       </c>
       <c r="R4" t="n">
-        <v>7295333</v>
+        <v>7295329</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122545728</v>
+        <v>122545726</v>
       </c>
       <c r="B5" t="n">
-        <v>78041</v>
+        <v>77592</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601927</v>
+        <v>601967</v>
       </c>
       <c r="R5" t="n">
         <v>7295329</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 34033-2023 artfynd.xlsx
+++ b/artfynd/A 34033-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122545731</v>
+        <v>122545726</v>
       </c>
       <c r="B2" t="n">
-        <v>56594</v>
+        <v>77592</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601928</v>
+        <v>601967</v>
       </c>
       <c r="R2" t="n">
-        <v>7295474</v>
+        <v>7295329</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122545730</v>
+        <v>122545731</v>
       </c>
       <c r="B3" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601927</v>
+        <v>601928</v>
       </c>
       <c r="R3" t="n">
-        <v>7295333</v>
+        <v>7295474</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122545728</v>
+        <v>122545730</v>
       </c>
       <c r="B4" t="n">
-        <v>78044</v>
+        <v>78660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,7 +942,7 @@
         <v>601927</v>
       </c>
       <c r="R4" t="n">
-        <v>7295329</v>
+        <v>7295333</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122545726</v>
+        <v>122545728</v>
       </c>
       <c r="B5" t="n">
-        <v>77592</v>
+        <v>78044</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601967</v>
+        <v>601927</v>
       </c>
       <c r="R5" t="n">
         <v>7295329</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 34033-2023 artfynd.xlsx
+++ b/artfynd/A 34033-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122545726</v>
+        <v>122545731</v>
       </c>
       <c r="B2" t="n">
-        <v>77694</v>
+        <v>56688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601967</v>
+        <v>601928</v>
       </c>
       <c r="R2" t="n">
-        <v>7295329</v>
+        <v>7295474</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122545728</v>
+        <v>122545730</v>
       </c>
       <c r="B3" t="n">
-        <v>78146</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,7 +830,7 @@
         <v>601927</v>
       </c>
       <c r="R3" t="n">
-        <v>7295329</v>
+        <v>7295333</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122545731</v>
+        <v>122545726</v>
       </c>
       <c r="B4" t="n">
-        <v>56688</v>
+        <v>77694</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601928</v>
+        <v>601967</v>
       </c>
       <c r="R4" t="n">
-        <v>7295474</v>
+        <v>7295329</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122545730</v>
+        <v>122545728</v>
       </c>
       <c r="B5" t="n">
-        <v>78762</v>
+        <v>78150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
         <v>601927</v>
       </c>
       <c r="R5" t="n">
-        <v>7295333</v>
+        <v>7295329</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 34033-2023 artfynd.xlsx
+++ b/artfynd/A 34033-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122545731</v>
+        <v>122545726</v>
       </c>
       <c r="B2" t="n">
-        <v>56688</v>
+        <v>77694</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601928</v>
+        <v>601967</v>
       </c>
       <c r="R2" t="n">
-        <v>7295474</v>
+        <v>7295329</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122545726</v>
+        <v>122545731</v>
       </c>
       <c r="B4" t="n">
-        <v>77694</v>
+        <v>56688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601967</v>
+        <v>601928</v>
       </c>
       <c r="R4" t="n">
-        <v>7295329</v>
+        <v>7295474</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 34033-2023 artfynd.xlsx
+++ b/artfynd/A 34033-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122545730</v>
+        <v>122545731</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601927</v>
+        <v>601928</v>
       </c>
       <c r="R3" t="n">
-        <v>7295333</v>
+        <v>7295474</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122545731</v>
+        <v>122545730</v>
       </c>
       <c r="B4" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601928</v>
+        <v>601927</v>
       </c>
       <c r="R4" t="n">
-        <v>7295474</v>
+        <v>7295333</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 34033-2023 artfynd.xlsx
+++ b/artfynd/A 34033-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122545731</v>
+        <v>122545730</v>
       </c>
       <c r="B3" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601928</v>
+        <v>601927</v>
       </c>
       <c r="R3" t="n">
-        <v>7295474</v>
+        <v>7295333</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122545730</v>
+        <v>122545731</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601927</v>
+        <v>601928</v>
       </c>
       <c r="R4" t="n">
-        <v>7295333</v>
+        <v>7295474</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
